--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -90,6 +90,12 @@
     <t>シンモラのピアス</t>
   </si>
   <si>
+    <t>スルトの指輪</t>
+  </si>
+  <si>
+    <t>Ring of Surtr</t>
+  </si>
+  <si>
     <t>雷の結晶</t>
   </si>
   <si>
@@ -120,6 +126,12 @@
     <t>放電の耳飾り</t>
   </si>
   <si>
+    <t>マグニのたすき</t>
+  </si>
+  <si>
+    <t>Magni's Focus Sash</t>
+  </si>
+  <si>
     <t>ブリザードアンク</t>
   </si>
   <si>
@@ -147,6 +159,12 @@
     <t>氷河の涙石</t>
   </si>
   <si>
+    <t>グラースティア</t>
+  </si>
+  <si>
+    <t>Glassterior</t>
+  </si>
+  <si>
     <t>アルフの光羽</t>
   </si>
   <si>
@@ -177,6 +195,12 @@
     <t>ダグの光冠</t>
   </si>
   <si>
+    <t>バルドルの輝石</t>
+  </si>
+  <si>
+    <t>Baldur's Glintstone</t>
+  </si>
+  <si>
     <t>邪神のリング</t>
   </si>
   <si>
@@ -205,6 +229,12 @@
   </si>
   <si>
     <t>フェンリルの牙</t>
+  </si>
+  <si>
+    <t>巨人王のモノクル</t>
+  </si>
+  <si>
+    <t>King's monocle</t>
   </si>
   <si>
     <t>新兵のバングル</t>
@@ -261,9 +291,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -282,22 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,8 +349,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,9 +387,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,24 +402,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,13 +412,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -404,22 +426,30 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,7 +464,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +530,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +608,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,127 +638,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -625,21 +655,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -669,6 +684,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -680,6 +704,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -701,30 +755,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -733,25 +763,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -760,118 +790,118 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1239,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1434,37 +1464,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" customFormat="1" spans="1:6">
       <c r="A9">
-        <v>2010</v>
+        <v>1130</v>
       </c>
       <c r="B9">
-        <v>2010</v>
+        <v>1130</v>
       </c>
       <c r="C9" t="str">
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>雷の結晶</v>
+        <v>スルトの指輪</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B10">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>トルドの雷針</v>
+        <v>雷の結晶</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1478,14 +1508,14 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B11">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C11" t="str">
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>雷神の指輪</v>
+        <v>トルドの雷針</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1497,16 +1527,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:6">
+    <row r="12" spans="1:6">
       <c r="A12">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B12">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>電撃のタリスマン</v>
+        <v>雷神の指輪</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1520,20 +1550,20 @@
     </row>
     <row r="13" customFormat="1" spans="1:6">
       <c r="A13">
-        <v>2110</v>
+        <v>2040</v>
       </c>
       <c r="B13">
-        <v>2110</v>
+        <v>2040</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
-        <v>トールズリング</v>
+        <v>電撃のタリスマン</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -1541,14 +1571,14 @@
     </row>
     <row r="14" customFormat="1" spans="1:6">
       <c r="A14">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="B14">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
-        <v>放電の耳飾り</v>
+        <v>トールズリング</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1560,58 +1590,58 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" customFormat="1" spans="1:6">
       <c r="A15">
-        <v>3010</v>
+        <v>2120</v>
       </c>
       <c r="B15">
-        <v>3010</v>
+        <v>2120</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>ブリザードアンク</v>
+        <v>放電の耳飾り</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:6">
       <c r="A16">
-        <v>3020</v>
+        <v>2130</v>
       </c>
       <c r="B16">
-        <v>3020</v>
+        <v>2130</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>氷風の耳飾り</v>
+        <v>マグニのたすき</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B17">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="C17" t="str">
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
-        <v>スヴェルの結界</v>
+        <v>ブリザードアンク</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1623,16 +1653,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:6">
+    <row r="18" spans="1:6">
       <c r="A18">
-        <v>3040</v>
+        <v>3020</v>
       </c>
       <c r="B18">
-        <v>3040</v>
+        <v>3020</v>
       </c>
       <c r="C18" t="str">
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
-        <v>巨人の首輪</v>
+        <v>氷風の耳飾り</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1644,12 +1674,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:6">
+    <row r="19" spans="1:6">
       <c r="A19">
-        <v>3110</v>
+        <v>3030</v>
       </c>
       <c r="B19">
-        <v>3110</v>
+        <v>3030</v>
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
@@ -1659,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -1667,98 +1697,98 @@
     </row>
     <row r="20" customFormat="1" spans="1:6">
       <c r="A20">
-        <v>3120</v>
+        <v>3040</v>
       </c>
       <c r="B20">
-        <v>3120</v>
+        <v>3040</v>
       </c>
       <c r="C20" t="str">
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
-        <v>氷河の涙石</v>
+        <v>巨人の首輪</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" customFormat="1" spans="1:6">
       <c r="A21">
-        <v>4010</v>
+        <v>3110</v>
       </c>
       <c r="B21">
-        <v>4010</v>
+        <v>3110</v>
       </c>
       <c r="C21" t="str">
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
-        <v>アルフの光羽</v>
+        <v>スヴェルの結界</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
       <c r="A22">
-        <v>4020</v>
+        <v>3120</v>
       </c>
       <c r="B22">
-        <v>4020</v>
+        <v>3120</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>聖光のリボン</v>
+        <v>氷河の涙石</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23">
-        <v>4030</v>
+        <v>3130</v>
       </c>
       <c r="B23">
-        <v>4030</v>
+        <v>3130</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>グリンの金剛毛</v>
+        <v>グラースティア</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="B24">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>アースブローチ</v>
+        <v>アルフの光羽</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -1770,43 +1800,43 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:6">
+    <row r="25" spans="1:6">
       <c r="A25">
-        <v>4110</v>
+        <v>4020</v>
       </c>
       <c r="B25">
-        <v>4110</v>
+        <v>4020</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>妖精の羽飾り</v>
+        <v>聖光のリボン</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:6">
+    <row r="26" spans="1:6">
       <c r="A26">
-        <v>4120</v>
+        <v>4030</v>
       </c>
       <c r="B26">
-        <v>4120</v>
+        <v>4030</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
-        <v>ダグの光冠</v>
+        <v>グリンの金剛毛</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -1814,295 +1844,400 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>5010</v>
+        <v>4040</v>
       </c>
       <c r="B27">
-        <v>5010</v>
+        <v>4040</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
-        <v>邪神のリング</v>
+        <v>アースブローチ</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
       <c r="A28">
-        <v>5020</v>
+        <v>4110</v>
       </c>
       <c r="B28">
-        <v>5020</v>
+        <v>4110</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>ヨルムの魔鱗</v>
+        <v>妖精の羽飾り</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:6">
       <c r="A29">
-        <v>5030</v>
+        <v>4120</v>
       </c>
       <c r="B29">
-        <v>5030</v>
+        <v>4120</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>ナグルファル片</v>
+        <v>ダグの光冠</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:6">
       <c r="A30">
-        <v>5040</v>
+        <v>4130</v>
       </c>
       <c r="B30">
-        <v>5040</v>
+        <v>4130</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
-        <v>ウートの幻影鏡</v>
+        <v>バルドルの輝石</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
-        <v>5110</v>
+        <v>5010</v>
       </c>
       <c r="B31">
-        <v>5110</v>
+        <v>5010</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
-        <v>影の腕輪</v>
+        <v>邪神のリング</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:6">
+    <row r="32" spans="1:6">
       <c r="A32">
-        <v>5120</v>
+        <v>5020</v>
       </c>
       <c r="B32">
-        <v>5120</v>
+        <v>5020</v>
       </c>
       <c r="C32" t="str">
         <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
-        <v>フェンリルの牙</v>
+        <v>ヨルムの魔鱗</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>5</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:6">
+    <row r="33" spans="1:6">
       <c r="A33">
-        <v>6010</v>
+        <v>5030</v>
       </c>
       <c r="B33">
-        <v>6010</v>
+        <v>5030</v>
       </c>
       <c r="C33" t="str">
         <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
-        <v>新兵のバングル</v>
+        <v>ナグルファル片</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:6">
       <c r="A34">
-        <v>6020</v>
+        <v>5040</v>
       </c>
       <c r="B34">
-        <v>6020</v>
+        <v>5040</v>
       </c>
       <c r="C34" t="str">
         <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
-        <v>炎のタリスマン</v>
+        <v>ウートの幻影鏡</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:6">
       <c r="A35">
-        <v>6030</v>
+        <v>5110</v>
       </c>
       <c r="B35">
-        <v>6030</v>
+        <v>5110</v>
       </c>
       <c r="C35" t="str">
         <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
-        <v>雷のタリスマン</v>
+        <v>影の腕輪</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:6">
       <c r="A36">
-        <v>6040</v>
+        <v>5120</v>
       </c>
       <c r="B36">
-        <v>6040</v>
+        <v>5120</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>氷のタリスマン</v>
+        <v>フェンリルの牙</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:6">
       <c r="A37">
-        <v>6050</v>
+        <v>5130</v>
       </c>
       <c r="B37">
-        <v>6050</v>
+        <v>5130</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>光のタリスマン</v>
+        <v>巨人王のモノクル</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:6">
       <c r="A38">
-        <v>6060</v>
+        <v>6010</v>
       </c>
       <c r="B38">
-        <v>6060</v>
+        <v>6010</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>闇のタリスマン</v>
+        <v>新兵のバングル</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:6">
       <c r="A39">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="B39">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>ルーンのエングレ</v>
+        <v>炎のタリスマン</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:6">
       <c r="A40">
-        <v>7020</v>
+        <v>6030</v>
       </c>
       <c r="B40">
-        <v>7020</v>
+        <v>6030</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
+        <v>雷のタリスマン</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:6">
+      <c r="A41">
+        <v>6040</v>
+      </c>
+      <c r="B41">
+        <v>6040</v>
+      </c>
+      <c r="C41" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
+        <v>氷のタリスマン</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:6">
+      <c r="A42">
+        <v>6050</v>
+      </c>
+      <c r="B42">
+        <v>6050</v>
+      </c>
+      <c r="C42" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
+        <v>光のタリスマン</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:6">
+      <c r="A43">
+        <v>6060</v>
+      </c>
+      <c r="B43">
+        <v>6060</v>
+      </c>
+      <c r="C43" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
+        <v>闇のタリスマン</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>7010</v>
+      </c>
+      <c r="B44">
+        <v>7010</v>
+      </c>
+      <c r="C44" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
+        <v>ルーンのエングレ</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44">
+        <v>11</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>7020</v>
+      </c>
+      <c r="B45">
+        <v>7020</v>
+      </c>
+      <c r="C45" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
         <v>ドヴェルグの指輪</v>
       </c>
-      <c r="D40">
+      <c r="D45">
         <v>6</v>
       </c>
-      <c r="E40">
+      <c r="E45">
         <v>11</v>
       </c>
-      <c r="F40">
+      <c r="F45">
         <v>6</v>
       </c>
     </row>
@@ -2116,7 +2251,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2280,38 +2415,38 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2010</v>
+        <v>1130</v>
       </c>
       <c r="B12">
-        <v>12010</v>
+        <v>1040</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:4">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>2010</v>
       </c>
       <c r="B13">
+        <v>12010</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:4">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14">
         <v>502010</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>2020</v>
-      </c>
-      <c r="B14">
-        <v>12020</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -2325,7 +2460,7 @@
         <v>2020</v>
       </c>
       <c r="B15">
-        <v>502020</v>
+        <v>12020</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -2336,10 +2471,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B16">
-        <v>12030</v>
+        <v>502020</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -2353,7 +2488,7 @@
         <v>2030</v>
       </c>
       <c r="B17">
-        <v>502030</v>
+        <v>12030</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -2364,10 +2499,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B18">
-        <v>12040</v>
+        <v>502030</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -2381,7 +2516,7 @@
         <v>2040</v>
       </c>
       <c r="B19">
-        <v>502040</v>
+        <v>12040</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -2392,13 +2527,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>2110</v>
+        <v>2040</v>
       </c>
       <c r="B20">
-        <v>2020</v>
+        <v>502040</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2406,10 +2541,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="B21">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -2420,13 +2555,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>3010</v>
+        <v>2120</v>
       </c>
       <c r="B22">
-        <v>13010</v>
+        <v>2030</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2434,13 +2569,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>3010</v>
+        <v>2130</v>
       </c>
       <c r="B23">
-        <v>503010</v>
+        <v>2040</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2448,10 +2583,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B24">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2462,10 +2597,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B25">
-        <v>503020</v>
+        <v>503010</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -2476,10 +2611,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B26">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -2490,10 +2625,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B27">
-        <v>503030</v>
+        <v>503020</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2504,10 +2639,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B28">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -2518,10 +2653,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B29">
-        <v>503040</v>
+        <v>503030</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -2532,13 +2667,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>3110</v>
+        <v>3040</v>
       </c>
       <c r="B30">
-        <v>3020</v>
+        <v>13040</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2546,13 +2681,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>3120</v>
+        <v>3040</v>
       </c>
       <c r="B31">
-        <v>3030</v>
+        <v>503040</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2560,13 +2695,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>4010</v>
+        <v>3110</v>
       </c>
       <c r="B32">
-        <v>14010</v>
+        <v>3020</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2574,13 +2709,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>4010</v>
+        <v>3120</v>
       </c>
       <c r="B33">
-        <v>504010</v>
+        <v>3030</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2588,13 +2723,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>4020</v>
+        <v>3130</v>
       </c>
       <c r="B34">
-        <v>14020</v>
+        <v>3040</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2602,10 +2737,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B35">
-        <v>504020</v>
+        <v>14010</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -2616,10 +2751,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>4030</v>
+        <v>4010</v>
       </c>
       <c r="B36">
-        <v>14030</v>
+        <v>504010</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -2630,10 +2765,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B37">
-        <v>504030</v>
+        <v>14020</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -2644,10 +2779,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>4040</v>
+        <v>4020</v>
       </c>
       <c r="B38">
-        <v>14040</v>
+        <v>504020</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -2658,10 +2793,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B39">
-        <v>504040</v>
+        <v>14030</v>
       </c>
       <c r="C39">
         <v>10</v>
@@ -2672,13 +2807,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>4110</v>
+        <v>4030</v>
       </c>
       <c r="B40">
-        <v>4020</v>
+        <v>504030</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2686,13 +2821,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>4120</v>
+        <v>4040</v>
       </c>
       <c r="B41">
-        <v>4030</v>
+        <v>14040</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2700,10 +2835,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>5010</v>
+        <v>4040</v>
       </c>
       <c r="B42">
-        <v>15010</v>
+        <v>504040</v>
       </c>
       <c r="C42">
         <v>10</v>
@@ -2714,13 +2849,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>5010</v>
+        <v>4110</v>
       </c>
       <c r="B43">
-        <v>505010</v>
+        <v>4020</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2728,13 +2863,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>5020</v>
+        <v>4120</v>
       </c>
       <c r="B44">
-        <v>15020</v>
+        <v>4030</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2742,13 +2877,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>5020</v>
+        <v>4130</v>
       </c>
       <c r="B45">
-        <v>505020</v>
+        <v>4040</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2756,10 +2891,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>5030</v>
+        <v>5010</v>
       </c>
       <c r="B46">
-        <v>15030</v>
+        <v>15010</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -2770,10 +2905,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>5030</v>
+        <v>5010</v>
       </c>
       <c r="B47">
-        <v>505030</v>
+        <v>505010</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2784,10 +2919,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="B48">
-        <v>15040</v>
+        <v>15020</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -2798,10 +2933,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="B49">
-        <v>505040</v>
+        <v>505020</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -2812,13 +2947,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>5110</v>
+        <v>5030</v>
       </c>
       <c r="B50">
-        <v>5020</v>
+        <v>15030</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2826,13 +2961,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>5120</v>
+        <v>5030</v>
       </c>
       <c r="B51">
-        <v>5030</v>
+        <v>505030</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2840,66 +2975,66 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>6010</v>
+        <v>5040</v>
       </c>
       <c r="B52">
-        <v>506010</v>
+        <v>15040</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>6010</v>
+        <v>5040</v>
       </c>
       <c r="B53">
-        <v>506011</v>
+        <v>505040</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>6010</v>
+        <v>5110</v>
       </c>
       <c r="B54">
-        <v>506012</v>
+        <v>5020</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>6010</v>
+        <v>5120</v>
       </c>
       <c r="B55">
-        <v>506013</v>
+        <v>5030</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>6020</v>
+        <v>5130</v>
       </c>
       <c r="B56">
-        <v>1010</v>
+        <v>5040</v>
       </c>
       <c r="C56">
         <v>8</v>
@@ -2910,24 +3045,24 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B57">
-        <v>506020</v>
+        <v>506010</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B58">
-        <v>11050</v>
+        <v>506011</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2938,52 +3073,52 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="B59">
-        <v>2010</v>
+        <v>506012</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="B60">
-        <v>506030</v>
+        <v>506013</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B61">
-        <v>12050</v>
+        <v>1010</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>6040</v>
+        <v>6020</v>
       </c>
       <c r="B62">
-        <v>3010</v>
+        <v>506020</v>
       </c>
       <c r="C62">
         <v>8</v>
@@ -2994,38 +3129,38 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>6040</v>
+        <v>6020</v>
       </c>
       <c r="B63">
-        <v>506040</v>
+        <v>11050</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="B64">
-        <v>13050</v>
+        <v>2010</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>6050</v>
+        <v>6030</v>
       </c>
       <c r="B65">
-        <v>4010</v>
+        <v>506030</v>
       </c>
       <c r="C65">
         <v>8</v>
@@ -3036,38 +3171,38 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>6050</v>
+        <v>6030</v>
       </c>
       <c r="B66">
-        <v>506050</v>
+        <v>12050</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>6050</v>
+        <v>6040</v>
       </c>
       <c r="B67">
-        <v>14050</v>
+        <v>3010</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>6060</v>
+        <v>6040</v>
       </c>
       <c r="B68">
-        <v>5010</v>
+        <v>506040</v>
       </c>
       <c r="C68">
         <v>8</v>
@@ -3078,83 +3213,138 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>6060</v>
+        <v>6040</v>
       </c>
       <c r="B69">
-        <v>506060</v>
+        <v>13050</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>6060</v>
+        <v>6050</v>
       </c>
       <c r="B70">
-        <v>15050</v>
+        <v>4010</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>7010</v>
+        <v>6050</v>
       </c>
       <c r="B71">
-        <v>507010</v>
+        <v>506050</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
+        <v>6050</v>
+      </c>
+      <c r="B72">
+        <v>14050</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73">
+        <v>6060</v>
+      </c>
+      <c r="B73">
+        <v>5010</v>
+      </c>
+      <c r="C73">
+        <v>8</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74">
+        <v>6060</v>
+      </c>
+      <c r="B74">
+        <v>506060</v>
+      </c>
+      <c r="C74">
+        <v>8</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75">
+        <v>6060</v>
+      </c>
+      <c r="B75">
+        <v>15050</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76">
+        <v>7010</v>
+      </c>
+      <c r="B76">
+        <v>507010</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77">
         <v>7020</v>
       </c>
-      <c r="B72">
+      <c r="B77">
         <v>507020</v>
       </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="3"/>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="3"/>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76"/>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77"/>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78"/>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79"/>
+      <c r="B79" s="3"/>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80"/>
+      <c r="B80" s="3"/>
     </row>
     <row r="81" spans="2:2">
       <c r="B81"/>
@@ -3232,10 +3422,10 @@
       <c r="B105"/>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="3"/>
+      <c r="B106"/>
     </row>
     <row r="107" spans="2:2">
-      <c r="B107" s="3"/>
+      <c r="B107"/>
     </row>
     <row r="108" spans="2:2">
       <c r="B108"/>
@@ -3247,10 +3437,25 @@
       <c r="B110"/>
     </row>
     <row r="111" spans="2:2">
-      <c r="B111"/>
+      <c r="B111" s="3"/>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112"/>
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3261,7 +3466,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
@@ -3373,32 +3578,32 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>2010</v>
+        <v>1130</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
       <c r="F9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
       <c r="F10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -3411,7 +3616,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -3424,7 +3629,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>2110</v>
+        <v>2040</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -3432,15 +3637,15 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -3450,32 +3655,33 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>3010</v>
+        <v>2120</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>3020</v>
+        <v>2130</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
       <c r="F16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
@@ -3488,70 +3694,70 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>3040</v>
+        <v>3020</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
       <c r="F18" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>3110</v>
+        <v>3030</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>3120</v>
+        <v>3040</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20"/>
+      <c r="E20" s="1"/>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>4010</v>
+        <v>3110</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>4020</v>
+        <v>3120</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1"/>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>4030</v>
+        <v>3130</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -3563,7 +3769,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="B24" t="s">
         <v>49</v>
@@ -3575,156 +3781,161 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>4110</v>
+        <v>4020</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="1"/>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>4120</v>
+        <v>4030</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1"/>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>5010</v>
+        <v>4040</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D27" s="1"/>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>5020</v>
+        <v>4110</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="1"/>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>5030</v>
+        <v>4120</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="F29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
-        <v>5040</v>
+        <v>4130</v>
       </c>
       <c r="B30" t="s">
         <v>59</v>
       </c>
+      <c r="D30" s="1"/>
       <c r="F30" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:6">
+    <row r="31" spans="1:6">
       <c r="A31">
-        <v>5110</v>
+        <v>5010</v>
       </c>
       <c r="B31" t="s">
         <v>61</v>
       </c>
       <c r="D31" s="1"/>
       <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
-        <v>5120</v>
+        <v>5020</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" s="1"/>
       <c r="F32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
-        <v>6010</v>
+        <v>5030</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:6">
       <c r="A34">
-        <v>6020</v>
+        <v>5040</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:6">
       <c r="A35">
-        <v>6030</v>
+        <v>5110</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D35" s="1"/>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:6">
       <c r="A36">
-        <v>6040</v>
+        <v>5120</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D36" s="1"/>
       <c r="F36" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:6">
       <c r="A37">
-        <v>6050</v>
+        <v>5130</v>
       </c>
       <c r="B37" t="s">
         <v>71</v>
       </c>
+      <c r="D37" s="1"/>
       <c r="F37" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:6">
       <c r="A38">
-        <v>6060</v>
+        <v>6010</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
@@ -3733,9 +3944,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" customFormat="1" spans="1:6">
       <c r="A39">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="B39" t="s">
         <v>75</v>
@@ -3744,15 +3955,70 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" customFormat="1" spans="1:6">
       <c r="A40">
-        <v>7020</v>
+        <v>6030</v>
       </c>
       <c r="B40" t="s">
         <v>77</v>
       </c>
       <c r="F40" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:6">
+      <c r="A41">
+        <v>6040</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:6">
+      <c r="A42">
+        <v>6050</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:6">
+      <c r="A43">
+        <v>6060</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>7010</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>7020</v>
+      </c>
+      <c r="B45" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -290,10 +290,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -319,6 +319,112 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -334,90 +440,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -426,30 +448,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -464,19 +464,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +518,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,109 +626,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,31 +644,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,6 +655,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -675,10 +690,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -687,8 +700,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -708,17 +721,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,24 +755,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -763,145 +763,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2251,7 +2251,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="B11">
-        <v>1030</v>
+        <v>501110</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="B12">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -2429,27 +2429,27 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2010</v>
+        <v>1120</v>
       </c>
       <c r="B13">
-        <v>12010</v>
+        <v>501120</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:4">
+    <row r="14" spans="1:4">
       <c r="A14">
-        <v>2010</v>
+        <v>1130</v>
       </c>
       <c r="B14">
-        <v>502010</v>
+        <v>1040</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2457,13 +2457,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>2020</v>
+        <v>1130</v>
       </c>
       <c r="B15">
-        <v>12020</v>
+        <v>501130</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B16">
-        <v>502020</v>
+        <v>12010</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -2483,12 +2483,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" customFormat="1" spans="1:4">
       <c r="A17">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="B17">
-        <v>12030</v>
+        <v>502010</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -2499,10 +2499,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B18">
-        <v>502030</v>
+        <v>12020</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>2040</v>
+        <v>2020</v>
       </c>
       <c r="B19">
-        <v>12040</v>
+        <v>502020</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B20">
-        <v>502040</v>
+        <v>12030</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>2110</v>
+        <v>2030</v>
       </c>
       <c r="B21">
-        <v>2020</v>
+        <v>502030</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2555,13 +2555,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>2120</v>
+        <v>2040</v>
       </c>
       <c r="B22">
-        <v>2030</v>
+        <v>12040</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="B23">
-        <v>2040</v>
+        <v>502040</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2583,13 +2583,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>3010</v>
+        <v>2110</v>
       </c>
       <c r="B24">
-        <v>13010</v>
+        <v>2020</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2597,13 +2597,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>3010</v>
+        <v>2110</v>
       </c>
       <c r="B25">
-        <v>503010</v>
+        <v>502110</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -2611,13 +2611,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>3020</v>
+        <v>2120</v>
       </c>
       <c r="B26">
-        <v>13020</v>
+        <v>2030</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>3020</v>
+        <v>2120</v>
       </c>
       <c r="B27">
-        <v>503020</v>
+        <v>502120</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2639,13 +2639,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>3030</v>
+        <v>2120</v>
       </c>
       <c r="B28">
-        <v>13030</v>
+        <v>502121</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2653,13 +2653,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>3030</v>
+        <v>2130</v>
       </c>
       <c r="B29">
-        <v>503030</v>
+        <v>2040</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2667,13 +2667,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>3040</v>
+        <v>2130</v>
       </c>
       <c r="B30">
-        <v>13040</v>
+        <v>502130</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>3040</v>
+        <v>3010</v>
       </c>
       <c r="B31">
-        <v>503040</v>
+        <v>13010</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -2695,13 +2695,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>3110</v>
+        <v>3010</v>
       </c>
       <c r="B32">
-        <v>3020</v>
+        <v>503010</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2709,13 +2709,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>3120</v>
+        <v>3020</v>
       </c>
       <c r="B33">
-        <v>3030</v>
+        <v>13020</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2723,13 +2723,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>3130</v>
+        <v>3020</v>
       </c>
       <c r="B34">
-        <v>3040</v>
+        <v>503020</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B35">
-        <v>14010</v>
+        <v>13030</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B36">
-        <v>504010</v>
+        <v>503030</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>4020</v>
+        <v>3040</v>
       </c>
       <c r="B37">
-        <v>14020</v>
+        <v>13040</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>4020</v>
+        <v>3040</v>
       </c>
       <c r="B38">
-        <v>504020</v>
+        <v>503040</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -2793,13 +2793,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>4030</v>
+        <v>3110</v>
       </c>
       <c r="B39">
-        <v>14030</v>
+        <v>3020</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>4030</v>
+        <v>3110</v>
       </c>
       <c r="B40">
-        <v>504030</v>
+        <v>503110</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2821,13 +2821,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>4040</v>
+        <v>3120</v>
       </c>
       <c r="B41">
-        <v>14040</v>
+        <v>3030</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2835,13 +2835,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>4040</v>
+        <v>3120</v>
       </c>
       <c r="B42">
-        <v>504040</v>
+        <v>503120</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>4110</v>
+        <v>3130</v>
       </c>
       <c r="B43">
-        <v>4020</v>
+        <v>3040</v>
       </c>
       <c r="C43">
         <v>8</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>4120</v>
+        <v>3130</v>
       </c>
       <c r="B44">
-        <v>4030</v>
+        <v>503130</v>
       </c>
       <c r="C44">
         <v>8</v>
@@ -2877,13 +2877,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>4130</v>
+        <v>4010</v>
       </c>
       <c r="B45">
-        <v>4040</v>
+        <v>14010</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B46">
-        <v>15010</v>
+        <v>504010</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="B47">
-        <v>505010</v>
+        <v>14020</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B48">
-        <v>15020</v>
+        <v>504020</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>5020</v>
+        <v>4030</v>
       </c>
       <c r="B49">
-        <v>505020</v>
+        <v>14030</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>5030</v>
+        <v>4030</v>
       </c>
       <c r="B50">
-        <v>15030</v>
+        <v>504030</v>
       </c>
       <c r="C50">
         <v>10</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>5030</v>
+        <v>4040</v>
       </c>
       <c r="B51">
-        <v>505030</v>
+        <v>14040</v>
       </c>
       <c r="C51">
         <v>10</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>5040</v>
+        <v>4040</v>
       </c>
       <c r="B52">
-        <v>15040</v>
+        <v>504040</v>
       </c>
       <c r="C52">
         <v>10</v>
@@ -2989,13 +2989,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>5040</v>
+        <v>4110</v>
       </c>
       <c r="B53">
-        <v>505040</v>
+        <v>4020</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>5110</v>
+        <v>4110</v>
       </c>
       <c r="B54">
-        <v>5020</v>
+        <v>504110</v>
       </c>
       <c r="C54">
         <v>8</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>5120</v>
+        <v>4120</v>
       </c>
       <c r="B55">
-        <v>5030</v>
+        <v>4030</v>
       </c>
       <c r="C55">
         <v>8</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>5130</v>
+        <v>4120</v>
       </c>
       <c r="B56">
-        <v>5040</v>
+        <v>504120</v>
       </c>
       <c r="C56">
         <v>8</v>
@@ -3045,69 +3045,69 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>6010</v>
+        <v>4130</v>
       </c>
       <c r="B57">
-        <v>506010</v>
+        <v>4040</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>6010</v>
+        <v>4130</v>
       </c>
       <c r="B58">
-        <v>506011</v>
+        <v>504130</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B59">
-        <v>506012</v>
+        <v>15010</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B60">
-        <v>506013</v>
+        <v>505010</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>6020</v>
+        <v>5020</v>
       </c>
       <c r="B61">
-        <v>1010</v>
+        <v>15020</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3115,13 +3115,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>6020</v>
+        <v>5020</v>
       </c>
       <c r="B62">
-        <v>506020</v>
+        <v>505020</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3129,27 +3129,27 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>6020</v>
+        <v>5030</v>
       </c>
       <c r="B63">
-        <v>11050</v>
+        <v>15030</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>6030</v>
+        <v>5030</v>
       </c>
       <c r="B64">
-        <v>2010</v>
+        <v>505030</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3157,13 +3157,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>6030</v>
+        <v>5040</v>
       </c>
       <c r="B65">
-        <v>506030</v>
+        <v>15040</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3171,24 +3171,24 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>6030</v>
+        <v>5040</v>
       </c>
       <c r="B66">
-        <v>12050</v>
+        <v>505040</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>6040</v>
+        <v>5110</v>
       </c>
       <c r="B67">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="C67">
         <v>8</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>6040</v>
+        <v>5110</v>
       </c>
       <c r="B68">
-        <v>506040</v>
+        <v>505110</v>
       </c>
       <c r="C68">
         <v>8</v>
@@ -3213,24 +3213,24 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>6040</v>
+        <v>5110</v>
       </c>
       <c r="B69">
-        <v>13050</v>
+        <v>505111</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>6050</v>
+        <v>5120</v>
       </c>
       <c r="B70">
-        <v>4010</v>
+        <v>5030</v>
       </c>
       <c r="C70">
         <v>8</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>6050</v>
+        <v>5120</v>
       </c>
       <c r="B71">
-        <v>506050</v>
+        <v>505120</v>
       </c>
       <c r="C71">
         <v>8</v>
@@ -3255,24 +3255,24 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>6050</v>
+        <v>5120</v>
       </c>
       <c r="B72">
-        <v>14050</v>
+        <v>505121</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>6060</v>
+        <v>5130</v>
       </c>
       <c r="B73">
-        <v>5010</v>
+        <v>5040</v>
       </c>
       <c r="C73">
         <v>8</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>6060</v>
+        <v>5130</v>
       </c>
       <c r="B74">
-        <v>506060</v>
+        <v>505130</v>
       </c>
       <c r="C74">
         <v>8</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>6060</v>
+        <v>6010</v>
       </c>
       <c r="B75">
-        <v>15050</v>
+        <v>506010</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>7010</v>
+        <v>6010</v>
       </c>
       <c r="B76">
-        <v>507010</v>
+        <v>506011</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3325,80 +3325,278 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
+        <v>6010</v>
+      </c>
+      <c r="B77">
+        <v>506012</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78">
+        <v>6010</v>
+      </c>
+      <c r="B78">
+        <v>506013</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79">
+        <v>6020</v>
+      </c>
+      <c r="B79">
+        <v>1010</v>
+      </c>
+      <c r="C79">
+        <v>8</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80">
+        <v>6020</v>
+      </c>
+      <c r="B80">
+        <v>506020</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81">
+        <v>6020</v>
+      </c>
+      <c r="B81">
+        <v>11050</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>6030</v>
+      </c>
+      <c r="B82">
+        <v>2010</v>
+      </c>
+      <c r="C82">
+        <v>8</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>6030</v>
+      </c>
+      <c r="B83">
+        <v>506030</v>
+      </c>
+      <c r="C83">
+        <v>8</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>6030</v>
+      </c>
+      <c r="B84">
+        <v>12050</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85">
+        <v>6040</v>
+      </c>
+      <c r="B85">
+        <v>3010</v>
+      </c>
+      <c r="C85">
+        <v>8</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86">
+        <v>6040</v>
+      </c>
+      <c r="B86">
+        <v>506040</v>
+      </c>
+      <c r="C86">
+        <v>8</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87">
+        <v>6040</v>
+      </c>
+      <c r="B87">
+        <v>13050</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88">
+        <v>6050</v>
+      </c>
+      <c r="B88">
+        <v>4010</v>
+      </c>
+      <c r="C88">
+        <v>8</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89">
+        <v>6050</v>
+      </c>
+      <c r="B89">
+        <v>506050</v>
+      </c>
+      <c r="C89">
+        <v>8</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90">
+        <v>6050</v>
+      </c>
+      <c r="B90">
+        <v>14050</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91">
+        <v>6060</v>
+      </c>
+      <c r="B91">
+        <v>5010</v>
+      </c>
+      <c r="C91">
+        <v>8</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92">
+        <v>6060</v>
+      </c>
+      <c r="B92">
+        <v>506060</v>
+      </c>
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93">
+        <v>6060</v>
+      </c>
+      <c r="B93">
+        <v>15050</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94">
+        <v>7010</v>
+      </c>
+      <c r="B94">
+        <v>507010</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95">
         <v>7020</v>
       </c>
-      <c r="B77">
+      <c r="B95">
         <v>507020</v>
       </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78"/>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="3"/>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="3"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84"/>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85"/>
-    </row>
-    <row r="86" spans="2:2">
-      <c r="B86"/>
-    </row>
-    <row r="87" spans="2:2">
-      <c r="B87"/>
-    </row>
-    <row r="88" spans="2:2">
-      <c r="B88"/>
-    </row>
-    <row r="89" spans="2:2">
-      <c r="B89"/>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90"/>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91"/>
-    </row>
-    <row r="92" spans="2:2">
-      <c r="B92"/>
-    </row>
-    <row r="93" spans="2:2">
-      <c r="B93"/>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94"/>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95"/>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96"/>
     </row>
     <row r="97" spans="2:2">
-      <c r="B97"/>
+      <c r="B97" s="3"/>
     </row>
     <row r="98" spans="2:2">
-      <c r="B98"/>
+      <c r="B98" s="3"/>
     </row>
     <row r="99" spans="2:2">
       <c r="B99"/>
@@ -3437,10 +3635,10 @@
       <c r="B110"/>
     </row>
     <row r="111" spans="2:2">
-      <c r="B111" s="3"/>
+      <c r="B111"/>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="3"/>
+      <c r="B112"/>
     </row>
     <row r="113" spans="2:2">
       <c r="B113"/>
@@ -3456,6 +3654,60 @@
     </row>
     <row r="117" spans="2:2">
       <c r="B117"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118"/>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119"/>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120"/>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121"/>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122"/>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123"/>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125"/>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126"/>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127"/>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131"/>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132"/>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133"/>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134"/>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -96,6 +96,18 @@
     <t>Ring of Surtr</t>
   </si>
   <si>
+    <t>ハールバルト</t>
+  </si>
+  <si>
+    <t>ファールバウティ</t>
+  </si>
+  <si>
+    <t>グリンカムビ</t>
+  </si>
+  <si>
+    <t>レーヴァテイン</t>
+  </si>
+  <si>
     <t>雷の結晶</t>
   </si>
   <si>
@@ -132,6 +144,18 @@
     <t>Magni's Focus Sash</t>
   </si>
   <si>
+    <t>ストームルーラー</t>
+  </si>
+  <si>
+    <t>雷鳴の手斧</t>
+  </si>
+  <si>
+    <t>電光石火のブーツ</t>
+  </si>
+  <si>
+    <t>光速の魔弓</t>
+  </si>
+  <si>
     <t>ブリザードアンク</t>
   </si>
   <si>
@@ -165,6 +189,18 @@
     <t>Glassterior</t>
   </si>
   <si>
+    <t>グレイシャー</t>
+  </si>
+  <si>
+    <t>吹雪の弓</t>
+  </si>
+  <si>
+    <t>ニヴルアヴァランチェ</t>
+  </si>
+  <si>
+    <t>エルト・カタラクト</t>
+  </si>
+  <si>
     <t>アルフの光羽</t>
   </si>
   <si>
@@ -201,6 +237,15 @@
     <t>Baldur's Glintstone</t>
   </si>
   <si>
+    <t>グングニル</t>
+  </si>
+  <si>
+    <t>ヴァルハラプレート</t>
+  </si>
+  <si>
+    <t>光紗のローブ</t>
+  </si>
+  <si>
     <t>邪神のリング</t>
   </si>
   <si>
@@ -235,6 +280,18 @@
   </si>
   <si>
     <t>King's monocle</t>
+  </si>
+  <si>
+    <t>漆黒の大鎌</t>
+  </si>
+  <si>
+    <t>スヴァルトアンブラ</t>
+  </si>
+  <si>
+    <t>幻影の外套</t>
+  </si>
+  <si>
+    <t>モラグバルのメイス</t>
   </si>
   <si>
     <t>新兵のバングル</t>
@@ -311,74 +368,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -387,51 +376,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -447,11 +391,124 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -464,13 +521,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,133 +689,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,7 +701,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,21 +712,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -697,15 +739,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -721,11 +754,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -755,6 +803,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -763,7 +820,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -772,136 +829,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1269,7 +1326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1485,688 +1542,688 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" customFormat="1" spans="1:6">
       <c r="A10">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B10">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>雷の結晶</v>
+        <v>ハールバルト</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
       <c r="A11">
-        <v>2020</v>
+        <v>1220</v>
       </c>
       <c r="B11">
-        <v>2020</v>
+        <v>1220</v>
       </c>
       <c r="C11" t="str">
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>トルドの雷針</v>
+        <v>ファールバウティ</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
       <c r="A12">
-        <v>2030</v>
+        <v>1230</v>
       </c>
       <c r="B12">
-        <v>2030</v>
+        <v>1230</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>雷神の指輪</v>
+        <v>グリンカムビ</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:6">
       <c r="A13">
-        <v>2040</v>
+        <v>1240</v>
       </c>
       <c r="B13">
-        <v>2040</v>
+        <v>1240</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
-        <v>電撃のタリスマン</v>
+        <v>レーヴァテイン</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
-        <v>2110</v>
+        <v>2010</v>
       </c>
       <c r="B14">
-        <v>2110</v>
+        <v>2010</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
-        <v>トールズリング</v>
+        <v>雷の結晶</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:6">
+    <row r="15" spans="1:6">
       <c r="A15">
-        <v>2120</v>
+        <v>2020</v>
       </c>
       <c r="B15">
-        <v>2120</v>
+        <v>2020</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>放電の耳飾り</v>
+        <v>トルドの雷針</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:6">
+    <row r="16" spans="1:6">
       <c r="A16">
-        <v>2130</v>
+        <v>2030</v>
       </c>
       <c r="B16">
-        <v>2130</v>
+        <v>2030</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>マグニのたすき</v>
+        <v>雷神の指輪</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" customFormat="1" spans="1:6">
       <c r="A17">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B17">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="C17" t="str">
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
-        <v>ブリザードアンク</v>
+        <v>電撃のタリスマン</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:6">
       <c r="A18">
-        <v>3020</v>
+        <v>2110</v>
       </c>
       <c r="B18">
-        <v>3020</v>
+        <v>2110</v>
       </c>
       <c r="C18" t="str">
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
-        <v>氷風の耳飾り</v>
+        <v>トールズリング</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:6">
       <c r="A19">
-        <v>3030</v>
+        <v>2120</v>
       </c>
       <c r="B19">
-        <v>3030</v>
+        <v>2120</v>
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
-        <v>スヴェルの結界</v>
+        <v>放電の耳飾り</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:6">
       <c r="A20">
-        <v>3040</v>
+        <v>2130</v>
       </c>
       <c r="B20">
-        <v>3040</v>
+        <v>2130</v>
       </c>
       <c r="C20" t="str">
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
-        <v>巨人の首輪</v>
+        <v>マグニのたすき</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:6">
       <c r="A21">
-        <v>3110</v>
+        <v>2210</v>
       </c>
       <c r="B21">
-        <v>3110</v>
+        <v>2210</v>
       </c>
       <c r="C21" t="str">
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
-        <v>スヴェルの結界</v>
+        <v>ストームルーラー</v>
       </c>
       <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
         <v>3</v>
       </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:6">
       <c r="A22">
-        <v>3120</v>
+        <v>2220</v>
       </c>
       <c r="B22">
-        <v>3120</v>
+        <v>2220</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>氷河の涙石</v>
+        <v>雷鳴の手斧</v>
       </c>
       <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
         <v>3</v>
       </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:6">
       <c r="A23">
-        <v>3130</v>
+        <v>2230</v>
       </c>
       <c r="B23">
-        <v>3130</v>
+        <v>2230</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>グラースティア</v>
+        <v>電光石火のブーツ</v>
       </c>
       <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
         <v>3</v>
       </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24">
-        <v>4010</v>
+        <v>2240</v>
       </c>
       <c r="B24">
-        <v>4010</v>
+        <v>2240</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>アルフの光羽</v>
+        <v>光速の魔弓</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="B25">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>聖光のリボン</v>
+        <v>ブリザードアンク</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>4030</v>
+        <v>3020</v>
       </c>
       <c r="B26">
-        <v>4030</v>
+        <v>3020</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
-        <v>グリンの金剛毛</v>
+        <v>氷風の耳飾り</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>4040</v>
+        <v>3030</v>
       </c>
       <c r="B27">
-        <v>4040</v>
+        <v>3030</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
-        <v>アースブローチ</v>
+        <v>スヴェルの結界</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:6">
       <c r="A28">
-        <v>4110</v>
+        <v>3040</v>
       </c>
       <c r="B28">
-        <v>4110</v>
+        <v>3040</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>妖精の羽飾り</v>
+        <v>巨人の首輪</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:6">
       <c r="A29">
-        <v>4120</v>
+        <v>3110</v>
       </c>
       <c r="B29">
-        <v>4120</v>
+        <v>3110</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>ダグの光冠</v>
+        <v>スヴェルの結界</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:6">
       <c r="A30">
-        <v>4130</v>
+        <v>3120</v>
       </c>
       <c r="B30">
-        <v>4130</v>
+        <v>3120</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
-        <v>バルドルの輝石</v>
+        <v>氷河の涙石</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
       <c r="A31">
-        <v>5010</v>
+        <v>3130</v>
       </c>
       <c r="B31">
-        <v>5010</v>
+        <v>3130</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
-        <v>邪神のリング</v>
+        <v>グラースティア</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
       <c r="A32">
-        <v>5020</v>
+        <v>3210</v>
       </c>
       <c r="B32">
-        <v>5020</v>
+        <v>3210</v>
       </c>
       <c r="C32" t="str">
         <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
-        <v>ヨルムの魔鱗</v>
+        <v>グレイシャー</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
       <c r="A33">
-        <v>5030</v>
+        <v>3220</v>
       </c>
       <c r="B33">
-        <v>5030</v>
+        <v>3220</v>
       </c>
       <c r="C33" t="str">
         <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
-        <v>ナグルファル片</v>
+        <v>吹雪の弓</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:6">
       <c r="A34">
-        <v>5040</v>
+        <v>3230</v>
       </c>
       <c r="B34">
-        <v>5040</v>
+        <v>3230</v>
       </c>
       <c r="C34" t="str">
         <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
-        <v>ウートの幻影鏡</v>
+        <v>ニヴルアヴァランチェ</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:6">
       <c r="A35">
-        <v>5110</v>
+        <v>3240</v>
       </c>
       <c r="B35">
-        <v>5110</v>
+        <v>3240</v>
       </c>
       <c r="C35" t="str">
         <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
-        <v>影の腕輪</v>
+        <v>エルト・カタラクト</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
-        <v>5120</v>
+        <v>4010</v>
       </c>
       <c r="B36">
-        <v>5120</v>
+        <v>4010</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>フェンリルの牙</v>
+        <v>アルフの光羽</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
-        <v>5130</v>
+        <v>4020</v>
       </c>
       <c r="B37">
-        <v>5130</v>
+        <v>4020</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>巨人王のモノクル</v>
+        <v>聖光のリボン</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
-        <v>6010</v>
+        <v>4030</v>
       </c>
       <c r="B38">
-        <v>6010</v>
+        <v>4030</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>新兵のバングル</v>
+        <v>グリンの金剛毛</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
-        <v>6020</v>
+        <v>4040</v>
       </c>
       <c r="B39">
-        <v>6020</v>
+        <v>4040</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>炎のタリスマン</v>
+        <v>アースブローチ</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:6">
       <c r="A40">
-        <v>6030</v>
+        <v>4110</v>
       </c>
       <c r="B40">
-        <v>6030</v>
+        <v>4110</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>雷のタリスマン</v>
+        <v>妖精の羽飾り</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:6">
       <c r="A41">
-        <v>6040</v>
+        <v>4120</v>
       </c>
       <c r="B41">
-        <v>6040</v>
+        <v>4120</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>氷のタリスマン</v>
+        <v>ダグの光冠</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:6">
       <c r="A42">
-        <v>6050</v>
+        <v>4130</v>
       </c>
       <c r="B42">
-        <v>6050</v>
+        <v>4130</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>光のタリスマン</v>
+        <v>バルドルの輝石</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2180,64 +2237,484 @@
     </row>
     <row r="43" customFormat="1" spans="1:6">
       <c r="A43">
-        <v>6060</v>
+        <v>4210</v>
       </c>
       <c r="B43">
-        <v>6060</v>
+        <v>4210</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>闇のタリスマン</v>
+        <v>グングニル</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:6">
       <c r="A44">
-        <v>7010</v>
+        <v>4220</v>
       </c>
       <c r="B44">
-        <v>7010</v>
+        <v>4220</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>ルーンのエングレ</v>
+        <v>ヴァルハラプレート</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:6">
       <c r="A45">
-        <v>7020</v>
+        <v>4230</v>
       </c>
       <c r="B45">
-        <v>7020</v>
+        <v>4230</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
+        <v>光紗のローブ</v>
+      </c>
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:6">
+      <c r="A46">
+        <v>4240</v>
+      </c>
+      <c r="B46">
+        <v>4240</v>
+      </c>
+      <c r="C46" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
+        <v>エルト・カタラクト</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>3</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>5010</v>
+      </c>
+      <c r="B47">
+        <v>5010</v>
+      </c>
+      <c r="C47" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
+        <v>邪神のリング</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>5020</v>
+      </c>
+      <c r="B48">
+        <v>5020</v>
+      </c>
+      <c r="C48" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
+        <v>ヨルムの魔鱗</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>5030</v>
+      </c>
+      <c r="B49">
+        <v>5030</v>
+      </c>
+      <c r="C49" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
+        <v>ナグルファル片</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:6">
+      <c r="A50">
+        <v>5040</v>
+      </c>
+      <c r="B50">
+        <v>5040</v>
+      </c>
+      <c r="C50" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
+        <v>ウートの幻影鏡</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:6">
+      <c r="A51">
+        <v>5110</v>
+      </c>
+      <c r="B51">
+        <v>5110</v>
+      </c>
+      <c r="C51" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
+        <v>影の腕輪</v>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:6">
+      <c r="A52">
+        <v>5120</v>
+      </c>
+      <c r="B52">
+        <v>5120</v>
+      </c>
+      <c r="C52" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
+        <v>フェンリルの牙</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:6">
+      <c r="A53">
+        <v>5130</v>
+      </c>
+      <c r="B53">
+        <v>5130</v>
+      </c>
+      <c r="C53" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
+        <v>巨人王のモノクル</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:6">
+      <c r="A54">
+        <v>5210</v>
+      </c>
+      <c r="B54">
+        <v>5210</v>
+      </c>
+      <c r="C54" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
+        <v>漆黒の大鎌</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:6">
+      <c r="A55">
+        <v>5220</v>
+      </c>
+      <c r="B55">
+        <v>5220</v>
+      </c>
+      <c r="C55" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
+        <v>スヴァルトアンブラ</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:6">
+      <c r="A56">
+        <v>5230</v>
+      </c>
+      <c r="B56">
+        <v>5230</v>
+      </c>
+      <c r="C56" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
+        <v>幻影の外套</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:6">
+      <c r="A57">
+        <v>5240</v>
+      </c>
+      <c r="B57">
+        <v>5240</v>
+      </c>
+      <c r="C57" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
+        <v>モラグバルのメイス</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:6">
+      <c r="A58">
+        <v>6010</v>
+      </c>
+      <c r="B58">
+        <v>6010</v>
+      </c>
+      <c r="C58" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
+        <v>新兵のバングル</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:6">
+      <c r="A59">
+        <v>6020</v>
+      </c>
+      <c r="B59">
+        <v>6020</v>
+      </c>
+      <c r="C59" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
+        <v>炎のタリスマン</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:6">
+      <c r="A60">
+        <v>6030</v>
+      </c>
+      <c r="B60">
+        <v>6030</v>
+      </c>
+      <c r="C60" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
+        <v>雷のタリスマン</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:6">
+      <c r="A61">
+        <v>6040</v>
+      </c>
+      <c r="B61">
+        <v>6040</v>
+      </c>
+      <c r="C61" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
+        <v>氷のタリスマン</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
+      <c r="A62">
+        <v>6050</v>
+      </c>
+      <c r="B62">
+        <v>6050</v>
+      </c>
+      <c r="C62" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
+        <v>光のタリスマン</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:6">
+      <c r="A63">
+        <v>6060</v>
+      </c>
+      <c r="B63">
+        <v>6060</v>
+      </c>
+      <c r="C63" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
+        <v>闇のタリスマン</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>7010</v>
+      </c>
+      <c r="B64">
+        <v>7010</v>
+      </c>
+      <c r="C64" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
+        <v>ルーンのエングレ</v>
+      </c>
+      <c r="D64">
+        <v>6</v>
+      </c>
+      <c r="E64">
+        <v>11</v>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>7020</v>
+      </c>
+      <c r="B65">
+        <v>7020</v>
+      </c>
+      <c r="C65" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
         <v>ドヴェルグの指輪</v>
       </c>
-      <c r="D45">
+      <c r="D65">
         <v>6</v>
       </c>
-      <c r="E45">
+      <c r="E65">
         <v>11</v>
       </c>
-      <c r="F45">
+      <c r="F65">
         <v>6</v>
       </c>
     </row>
@@ -2251,7 +2728,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2471,27 +2948,27 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B16">
-        <v>12010</v>
+        <v>11110</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:4">
+    <row r="17" spans="1:4">
       <c r="A17">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B17">
-        <v>502010</v>
+        <v>501210</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2499,13 +2976,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>2020</v>
+        <v>1220</v>
       </c>
       <c r="B18">
-        <v>12020</v>
+        <v>11120</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2513,13 +2990,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>2020</v>
+        <v>1220</v>
       </c>
       <c r="B19">
-        <v>502020</v>
+        <v>501220</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2527,13 +3004,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>2030</v>
+        <v>1230</v>
       </c>
       <c r="B20">
-        <v>12030</v>
+        <v>11130</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2541,13 +3018,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>2030</v>
+        <v>1230</v>
       </c>
       <c r="B21">
-        <v>502030</v>
+        <v>501230</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2555,13 +3032,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>2040</v>
+        <v>1240</v>
       </c>
       <c r="B22">
-        <v>12040</v>
+        <v>11140</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2569,13 +3046,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>2040</v>
+        <v>1240</v>
       </c>
       <c r="B23">
-        <v>502040</v>
+        <v>501240</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2583,27 +3060,27 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>2110</v>
+        <v>2010</v>
       </c>
       <c r="B24">
-        <v>2020</v>
+        <v>12010</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" customFormat="1" spans="1:4">
       <c r="A25">
-        <v>2110</v>
+        <v>2010</v>
       </c>
       <c r="B25">
-        <v>502110</v>
+        <v>502010</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -2611,13 +3088,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>2120</v>
+        <v>2020</v>
       </c>
       <c r="B26">
-        <v>2030</v>
+        <v>12020</v>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2625,13 +3102,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>2120</v>
+        <v>2020</v>
       </c>
       <c r="B27">
-        <v>502120</v>
+        <v>502020</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2639,13 +3116,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>2120</v>
+        <v>2030</v>
       </c>
       <c r="B28">
-        <v>502121</v>
+        <v>12030</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2653,13 +3130,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>2130</v>
+        <v>2030</v>
       </c>
       <c r="B29">
-        <v>2040</v>
+        <v>502030</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2667,13 +3144,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="B30">
-        <v>502130</v>
+        <v>12040</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2681,10 +3158,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B31">
-        <v>13010</v>
+        <v>502040</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -2695,13 +3172,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>3010</v>
+        <v>2110</v>
       </c>
       <c r="B32">
-        <v>503010</v>
+        <v>2020</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2709,13 +3186,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>3020</v>
+        <v>2110</v>
       </c>
       <c r="B33">
-        <v>13020</v>
+        <v>502110</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2723,13 +3200,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>3020</v>
+        <v>2120</v>
       </c>
       <c r="B34">
-        <v>503020</v>
+        <v>2030</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2737,13 +3214,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>3030</v>
+        <v>2120</v>
       </c>
       <c r="B35">
-        <v>13030</v>
+        <v>502120</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2751,13 +3228,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>3030</v>
+        <v>2120</v>
       </c>
       <c r="B36">
-        <v>503030</v>
+        <v>502121</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2765,13 +3242,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>3040</v>
+        <v>2130</v>
       </c>
       <c r="B37">
-        <v>13040</v>
+        <v>2040</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2779,13 +3256,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>3040</v>
+        <v>2130</v>
       </c>
       <c r="B38">
-        <v>503040</v>
+        <v>502130</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2793,27 +3270,27 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>3110</v>
+        <v>2210</v>
       </c>
       <c r="B39">
-        <v>3020</v>
+        <v>12110</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" customFormat="1" spans="1:4">
       <c r="A40">
-        <v>3110</v>
+        <v>2210</v>
       </c>
       <c r="B40">
-        <v>503110</v>
+        <v>502210</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2821,13 +3298,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>3120</v>
+        <v>2220</v>
       </c>
       <c r="B41">
-        <v>3030</v>
+        <v>12120</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2835,13 +3312,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>3120</v>
+        <v>2220</v>
       </c>
       <c r="B42">
-        <v>503120</v>
+        <v>502220</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2849,13 +3326,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>3130</v>
+        <v>2230</v>
       </c>
       <c r="B43">
-        <v>3040</v>
+        <v>12130</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2863,13 +3340,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>3130</v>
+        <v>2230</v>
       </c>
       <c r="B44">
-        <v>503130</v>
+        <v>502230</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2877,13 +3354,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>4010</v>
+        <v>2240</v>
       </c>
       <c r="B45">
-        <v>14010</v>
+        <v>12140</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2891,13 +3368,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>4010</v>
+        <v>2240</v>
       </c>
       <c r="B46">
-        <v>504010</v>
+        <v>502240</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2905,10 +3382,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="B47">
-        <v>14020</v>
+        <v>13010</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2919,10 +3396,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="B48">
-        <v>504020</v>
+        <v>503010</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -2933,10 +3410,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>4030</v>
+        <v>3020</v>
       </c>
       <c r="B49">
-        <v>14030</v>
+        <v>13020</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -2947,10 +3424,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>4030</v>
+        <v>3020</v>
       </c>
       <c r="B50">
-        <v>504030</v>
+        <v>503020</v>
       </c>
       <c r="C50">
         <v>10</v>
@@ -2961,10 +3438,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>4040</v>
+        <v>3030</v>
       </c>
       <c r="B51">
-        <v>14040</v>
+        <v>13030</v>
       </c>
       <c r="C51">
         <v>10</v>
@@ -2975,10 +3452,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>4040</v>
+        <v>3030</v>
       </c>
       <c r="B52">
-        <v>504040</v>
+        <v>503030</v>
       </c>
       <c r="C52">
         <v>10</v>
@@ -2989,13 +3466,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>4110</v>
+        <v>3040</v>
       </c>
       <c r="B53">
-        <v>4020</v>
+        <v>13040</v>
       </c>
       <c r="C53">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3003,13 +3480,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>4110</v>
+        <v>3040</v>
       </c>
       <c r="B54">
-        <v>504110</v>
+        <v>503040</v>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3017,10 +3494,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>4120</v>
+        <v>3110</v>
       </c>
       <c r="B55">
-        <v>4030</v>
+        <v>3020</v>
       </c>
       <c r="C55">
         <v>8</v>
@@ -3031,10 +3508,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>4120</v>
+        <v>3110</v>
       </c>
       <c r="B56">
-        <v>504120</v>
+        <v>503110</v>
       </c>
       <c r="C56">
         <v>8</v>
@@ -3045,10 +3522,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>4130</v>
+        <v>3120</v>
       </c>
       <c r="B57">
-        <v>4040</v>
+        <v>3030</v>
       </c>
       <c r="C57">
         <v>8</v>
@@ -3059,10 +3536,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>4130</v>
+        <v>3120</v>
       </c>
       <c r="B58">
-        <v>504130</v>
+        <v>503120</v>
       </c>
       <c r="C58">
         <v>8</v>
@@ -3073,13 +3550,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>5010</v>
+        <v>3130</v>
       </c>
       <c r="B59">
-        <v>15010</v>
+        <v>3040</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3087,13 +3564,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>5010</v>
+        <v>3130</v>
       </c>
       <c r="B60">
-        <v>505010</v>
+        <v>503130</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3101,13 +3578,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>5020</v>
+        <v>3210</v>
       </c>
       <c r="B61">
-        <v>15020</v>
+        <v>13110</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3115,13 +3592,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>5020</v>
+        <v>3210</v>
       </c>
       <c r="B62">
-        <v>505020</v>
+        <v>503210</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3129,13 +3606,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>5030</v>
+        <v>3220</v>
       </c>
       <c r="B63">
-        <v>15030</v>
+        <v>13120</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3143,13 +3620,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>5030</v>
+        <v>3220</v>
       </c>
       <c r="B64">
-        <v>505030</v>
+        <v>503220</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3157,13 +3634,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>5040</v>
+        <v>3230</v>
       </c>
       <c r="B65">
-        <v>15040</v>
+        <v>13130</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3171,13 +3648,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>5040</v>
+        <v>3230</v>
       </c>
       <c r="B66">
-        <v>505040</v>
+        <v>503230</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3185,13 +3662,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>5110</v>
+        <v>3240</v>
       </c>
       <c r="B67">
-        <v>5020</v>
+        <v>13140</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3199,13 +3676,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>5110</v>
+        <v>3240</v>
       </c>
       <c r="B68">
-        <v>505110</v>
+        <v>503240</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3213,13 +3690,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>5110</v>
+        <v>4010</v>
       </c>
       <c r="B69">
-        <v>505111</v>
+        <v>14010</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3227,13 +3704,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>5120</v>
+        <v>4010</v>
       </c>
       <c r="B70">
-        <v>5030</v>
+        <v>504010</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3241,13 +3718,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>5120</v>
+        <v>4020</v>
       </c>
       <c r="B71">
-        <v>505120</v>
+        <v>14020</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3255,13 +3732,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>5120</v>
+        <v>4020</v>
       </c>
       <c r="B72">
-        <v>505121</v>
+        <v>504020</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3269,13 +3746,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>5130</v>
+        <v>4030</v>
       </c>
       <c r="B73">
-        <v>5040</v>
+        <v>14030</v>
       </c>
       <c r="C73">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3283,13 +3760,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>5130</v>
+        <v>4030</v>
       </c>
       <c r="B74">
-        <v>505130</v>
+        <v>504030</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3297,66 +3774,66 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>6010</v>
+        <v>4040</v>
       </c>
       <c r="B75">
-        <v>506010</v>
+        <v>14040</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>6010</v>
+        <v>4040</v>
       </c>
       <c r="B76">
-        <v>506011</v>
+        <v>504040</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>6010</v>
+        <v>4110</v>
       </c>
       <c r="B77">
-        <v>506012</v>
+        <v>4020</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>6010</v>
+        <v>4110</v>
       </c>
       <c r="B78">
-        <v>506013</v>
+        <v>504110</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>6020</v>
+        <v>4120</v>
       </c>
       <c r="B79">
-        <v>1010</v>
+        <v>4030</v>
       </c>
       <c r="C79">
         <v>8</v>
@@ -3367,10 +3844,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>6020</v>
+        <v>4120</v>
       </c>
       <c r="B80">
-        <v>506020</v>
+        <v>504120</v>
       </c>
       <c r="C80">
         <v>8</v>
@@ -3381,24 +3858,24 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>6020</v>
+        <v>4130</v>
       </c>
       <c r="B81">
-        <v>11050</v>
+        <v>4040</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>6030</v>
+        <v>4130</v>
       </c>
       <c r="B82">
-        <v>2010</v>
+        <v>504130</v>
       </c>
       <c r="C82">
         <v>8</v>
@@ -3409,13 +3886,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>6030</v>
+        <v>4210</v>
       </c>
       <c r="B83">
-        <v>506030</v>
+        <v>14110</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3423,27 +3900,27 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>6030</v>
+        <v>4210</v>
       </c>
       <c r="B84">
-        <v>12050</v>
+        <v>504210</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>6040</v>
+        <v>4220</v>
       </c>
       <c r="B85">
-        <v>3010</v>
+        <v>14120</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3451,13 +3928,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>6040</v>
+        <v>4220</v>
       </c>
       <c r="B86">
-        <v>506040</v>
+        <v>504220</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3465,27 +3942,27 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>6040</v>
+        <v>4230</v>
       </c>
       <c r="B87">
-        <v>13050</v>
+        <v>14130</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>6050</v>
+        <v>4230</v>
       </c>
       <c r="B88">
-        <v>4010</v>
+        <v>504230</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3493,13 +3970,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>6050</v>
+        <v>4240</v>
       </c>
       <c r="B89">
-        <v>506050</v>
+        <v>14140</v>
       </c>
       <c r="C89">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3507,27 +3984,27 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>6050</v>
+        <v>4240</v>
       </c>
       <c r="B90">
-        <v>14050</v>
+        <v>504240</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>6060</v>
+        <v>5010</v>
       </c>
       <c r="B91">
-        <v>5010</v>
+        <v>15010</v>
       </c>
       <c r="C91">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3535,13 +4012,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>6060</v>
+        <v>5010</v>
       </c>
       <c r="B92">
-        <v>506060</v>
+        <v>505010</v>
       </c>
       <c r="C92">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3549,165 +4026,725 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>6060</v>
+        <v>5020</v>
       </c>
       <c r="B93">
-        <v>15050</v>
+        <v>15020</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>7010</v>
+        <v>5020</v>
       </c>
       <c r="B94">
-        <v>507010</v>
+        <v>505020</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
+        <v>5030</v>
+      </c>
+      <c r="B95">
+        <v>15030</v>
+      </c>
+      <c r="C95">
+        <v>10</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96">
+        <v>5030</v>
+      </c>
+      <c r="B96">
+        <v>505030</v>
+      </c>
+      <c r="C96">
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97">
+        <v>5040</v>
+      </c>
+      <c r="B97">
+        <v>15040</v>
+      </c>
+      <c r="C97">
+        <v>10</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98">
+        <v>5040</v>
+      </c>
+      <c r="B98">
+        <v>505040</v>
+      </c>
+      <c r="C98">
+        <v>10</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99">
+        <v>5110</v>
+      </c>
+      <c r="B99">
+        <v>5020</v>
+      </c>
+      <c r="C99">
+        <v>8</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100">
+        <v>5110</v>
+      </c>
+      <c r="B100">
+        <v>505110</v>
+      </c>
+      <c r="C100">
+        <v>8</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101">
+        <v>5110</v>
+      </c>
+      <c r="B101">
+        <v>505111</v>
+      </c>
+      <c r="C101">
+        <v>8</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102">
+        <v>5120</v>
+      </c>
+      <c r="B102">
+        <v>5030</v>
+      </c>
+      <c r="C102">
+        <v>8</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103">
+        <v>5120</v>
+      </c>
+      <c r="B103">
+        <v>505120</v>
+      </c>
+      <c r="C103">
+        <v>8</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104">
+        <v>5120</v>
+      </c>
+      <c r="B104">
+        <v>505121</v>
+      </c>
+      <c r="C104">
+        <v>8</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105">
+        <v>5130</v>
+      </c>
+      <c r="B105">
+        <v>5040</v>
+      </c>
+      <c r="C105">
+        <v>8</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106">
+        <v>5130</v>
+      </c>
+      <c r="B106">
+        <v>505130</v>
+      </c>
+      <c r="C106">
+        <v>8</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107">
+        <v>5210</v>
+      </c>
+      <c r="B107">
+        <v>15110</v>
+      </c>
+      <c r="C107">
+        <v>5</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108">
+        <v>5210</v>
+      </c>
+      <c r="B108">
+        <v>505210</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109">
+        <v>5220</v>
+      </c>
+      <c r="B109">
+        <v>15120</v>
+      </c>
+      <c r="C109">
+        <v>5</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110">
+        <v>5220</v>
+      </c>
+      <c r="B110">
+        <v>505220</v>
+      </c>
+      <c r="C110">
+        <v>5</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111">
+        <v>5230</v>
+      </c>
+      <c r="B111">
+        <v>15130</v>
+      </c>
+      <c r="C111">
+        <v>5</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112">
+        <v>5230</v>
+      </c>
+      <c r="B112">
+        <v>505230</v>
+      </c>
+      <c r="C112">
+        <v>5</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113">
+        <v>5240</v>
+      </c>
+      <c r="B113">
+        <v>15140</v>
+      </c>
+      <c r="C113">
+        <v>5</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114">
+        <v>5240</v>
+      </c>
+      <c r="B114">
+        <v>505240</v>
+      </c>
+      <c r="C114">
+        <v>5</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115">
+        <v>6010</v>
+      </c>
+      <c r="B115">
+        <v>506010</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116">
+        <v>6010</v>
+      </c>
+      <c r="B116">
+        <v>506011</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117">
+        <v>6010</v>
+      </c>
+      <c r="B117">
+        <v>506012</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118">
+        <v>6010</v>
+      </c>
+      <c r="B118">
+        <v>506013</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119">
+        <v>6020</v>
+      </c>
+      <c r="B119">
+        <v>1010</v>
+      </c>
+      <c r="C119">
+        <v>8</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120">
+        <v>6020</v>
+      </c>
+      <c r="B120">
+        <v>506020</v>
+      </c>
+      <c r="C120">
+        <v>8</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121">
+        <v>6020</v>
+      </c>
+      <c r="B121">
+        <v>11050</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122">
+        <v>6030</v>
+      </c>
+      <c r="B122">
+        <v>2010</v>
+      </c>
+      <c r="C122">
+        <v>8</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123">
+        <v>6030</v>
+      </c>
+      <c r="B123">
+        <v>506030</v>
+      </c>
+      <c r="C123">
+        <v>8</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124">
+        <v>6030</v>
+      </c>
+      <c r="B124">
+        <v>12050</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125">
+        <v>6040</v>
+      </c>
+      <c r="B125">
+        <v>3010</v>
+      </c>
+      <c r="C125">
+        <v>8</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126">
+        <v>6040</v>
+      </c>
+      <c r="B126">
+        <v>506040</v>
+      </c>
+      <c r="C126">
+        <v>8</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127">
+        <v>6040</v>
+      </c>
+      <c r="B127">
+        <v>13050</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128">
+        <v>6050</v>
+      </c>
+      <c r="B128">
+        <v>4010</v>
+      </c>
+      <c r="C128">
+        <v>8</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129">
+        <v>6050</v>
+      </c>
+      <c r="B129">
+        <v>506050</v>
+      </c>
+      <c r="C129">
+        <v>8</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130">
+        <v>6050</v>
+      </c>
+      <c r="B130">
+        <v>14050</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131">
+        <v>6060</v>
+      </c>
+      <c r="B131">
+        <v>5010</v>
+      </c>
+      <c r="C131">
+        <v>8</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132">
+        <v>6060</v>
+      </c>
+      <c r="B132">
+        <v>506060</v>
+      </c>
+      <c r="C132">
+        <v>8</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133">
+        <v>6060</v>
+      </c>
+      <c r="B133">
+        <v>15050</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134">
+        <v>7010</v>
+      </c>
+      <c r="B134">
+        <v>507010</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135">
         <v>7020</v>
       </c>
-      <c r="B95">
+      <c r="B135">
         <v>507020</v>
       </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96"/>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="3"/>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="3"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99"/>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100"/>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101"/>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102"/>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103"/>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105"/>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106"/>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107"/>
-    </row>
-    <row r="108" spans="2:2">
-      <c r="B108"/>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109"/>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112"/>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115"/>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116"/>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117"/>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118"/>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119"/>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120"/>
-    </row>
-    <row r="121" spans="2:2">
-      <c r="B121"/>
-    </row>
-    <row r="122" spans="2:2">
-      <c r="B122"/>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123"/>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124"/>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125"/>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126"/>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127"/>
-    </row>
-    <row r="128" spans="2:2">
-      <c r="B128"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="3"/>
-    </row>
-    <row r="130" spans="2:2">
-      <c r="B130" s="3"/>
-    </row>
-    <row r="131" spans="2:2">
-      <c r="B131"/>
-    </row>
-    <row r="132" spans="2:2">
-      <c r="B132"/>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133"/>
-    </row>
-    <row r="134" spans="2:2">
-      <c r="B134"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135"/>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136"/>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139"/>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140"/>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141"/>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142"/>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143"/>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144"/>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145"/>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146"/>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147"/>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148"/>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149"/>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150"/>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151"/>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152"/>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153"/>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154"/>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155"/>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156"/>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157"/>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158"/>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159"/>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160"/>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161"/>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162"/>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163"/>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164"/>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165"/>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166"/>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167"/>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168"/>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171"/>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172"/>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173"/>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174"/>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3718,7 +4755,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
@@ -3841,76 +4878,65 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:5">
       <c r="A10">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="F10" t="s">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>1220</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>2020</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" customFormat="1" spans="1:5">
       <c r="A12">
-        <v>2030</v>
+        <v>1230</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C12"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
-        <v>2040</v>
+        <v>1240</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>2110</v>
+        <v>2010</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
       <c r="F14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>2120</v>
+        <v>2020</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -3920,357 +4946,572 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>2130</v>
+        <v>2030</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>3020</v>
+        <v>2110</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>3030</v>
+        <v>2120</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>3040</v>
+        <v>2130</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:5">
       <c r="A21">
-        <v>3110</v>
+        <v>2210</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
+      <c r="C21"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" customFormat="1" spans="1:5">
       <c r="A22">
-        <v>3120</v>
+        <v>2220</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C22"/>
       <c r="D22" s="1"/>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:5">
       <c r="A23">
-        <v>3130</v>
+        <v>2230</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D23" s="1"/>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:5">
       <c r="A24">
-        <v>4010</v>
+        <v>2240</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C24"/>
       <c r="D24" s="1"/>
-      <c r="F24" t="s">
-        <v>50</v>
-      </c>
+      <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>4030</v>
+        <v>3020</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D26" s="1"/>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>4040</v>
+        <v>3030</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>4110</v>
+        <v>3040</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>4120</v>
+        <v>3110</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>4130</v>
+        <v>3120</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D30" s="1"/>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>5010</v>
+        <v>3130</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D31" s="1"/>
       <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:5">
       <c r="A32">
-        <v>5020</v>
+        <v>3210</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:5">
       <c r="A33">
-        <v>5030</v>
+        <v>3220</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:6">
+        <v>58</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:5">
       <c r="A34">
-        <v>5040</v>
+        <v>3230</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:6">
+        <v>59</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" customFormat="1" spans="1:5">
       <c r="A35">
-        <v>5110</v>
+        <v>3240</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:6">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
-        <v>5120</v>
+        <v>4010</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D36" s="1"/>
       <c r="F36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
-        <v>5130</v>
+        <v>4020</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1"/>
       <c r="F37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>4030</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="F38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>4040</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="F39" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>4110</v>
+      </c>
+      <c r="B40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>4120</v>
+      </c>
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="F41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>4130</v>
+      </c>
+      <c r="B42" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="F42" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:6">
-      <c r="A38">
+    <row r="43" customFormat="1" spans="1:5">
+      <c r="A43">
+        <v>4210</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" spans="1:5">
+      <c r="A44">
+        <v>4220</v>
+      </c>
+      <c r="B44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" customFormat="1" spans="1:5">
+      <c r="A45">
+        <v>4230</v>
+      </c>
+      <c r="B45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" customFormat="1" spans="1:5">
+      <c r="A46">
+        <v>4240</v>
+      </c>
+      <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>5010</v>
+      </c>
+      <c r="B47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="F47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>5020</v>
+      </c>
+      <c r="B48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="F48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>5030</v>
+      </c>
+      <c r="B49" t="s">
+        <v>80</v>
+      </c>
+      <c r="F49" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:6">
+      <c r="A50">
+        <v>5040</v>
+      </c>
+      <c r="B50" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:6">
+      <c r="A51">
+        <v>5110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="F51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:6">
+      <c r="A52">
+        <v>5120</v>
+      </c>
+      <c r="B52" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="F52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:6">
+      <c r="A53">
+        <v>5130</v>
+      </c>
+      <c r="B53" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="F53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:5">
+      <c r="A54">
+        <v>5210</v>
+      </c>
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" customFormat="1" spans="1:5">
+      <c r="A55">
+        <v>5220</v>
+      </c>
+      <c r="B55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" customFormat="1" spans="1:5">
+      <c r="A56">
+        <v>5230</v>
+      </c>
+      <c r="B56" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" customFormat="1" spans="1:5">
+      <c r="A57">
+        <v>5240</v>
+      </c>
+      <c r="B57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" customFormat="1" spans="1:6">
+      <c r="A58">
         <v>6010</v>
       </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:6">
-      <c r="A39">
+      <c r="B58" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:6">
+      <c r="A59">
         <v>6020</v>
       </c>
-      <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:6">
-      <c r="A40">
+      <c r="B59" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:6">
+      <c r="A60">
         <v>6030</v>
       </c>
-      <c r="B40" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:6">
-      <c r="A41">
+      <c r="B60" t="s">
+        <v>96</v>
+      </c>
+      <c r="F60" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:6">
+      <c r="A61">
         <v>6040</v>
       </c>
-      <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:6">
-      <c r="A42">
+      <c r="B61" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
+      <c r="A62">
         <v>6050</v>
       </c>
-      <c r="B42" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:6">
-      <c r="A43">
+      <c r="B62" t="s">
+        <v>100</v>
+      </c>
+      <c r="F62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:6">
+      <c r="A63">
         <v>6060</v>
       </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
+      <c r="B63" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
         <v>7010</v>
       </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
+      <c r="B64" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
         <v>7020</v>
       </c>
-      <c r="B45" t="s">
-        <v>87</v>
-      </c>
-      <c r="F45" t="s">
-        <v>88</v>
+      <c r="B65" t="s">
+        <v>106</v>
+      </c>
+      <c r="F65" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
